--- a/results/reliability_eval/Llama-3-8B_P1376_sample_30_tokens_0.1_temp_factual_retrieval_scores_08-24-4.xlsx
+++ b/results/reliability_eval/Llama-3-8B_P1376_sample_30_tokens_0.1_temp_factual_retrieval_scores_08-24-4.xlsx
@@ -477,31 +477,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.5537964245662643</v>
+        <v>0.3847972793453425</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8577476611834531</v>
+        <v>0.8868067881774931</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5535252252054151</v>
+        <v>0.3848304904617674</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8575806062548614</v>
+        <v>0.8868074041623372</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4438800565853802</v>
+        <v>0.6221637706573144</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8034640101352841</v>
+        <v>0.9421581711134313</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9939126738058066</v>
+        <v>0.9975025240448483</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9985488355044748</v>
+        <v>0.9996952130404222</v>
       </c>
       <c r="I2" t="n">
-        <v>0.837</v>
+        <v>0.918</v>
       </c>
     </row>
   </sheetData>
